--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1029"/>
+  <dimension ref="A1:L1032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56240,6 +56240,182 @@
         </is>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>41821498_Bioorthogonal Click-Engineered Microneedle Patch E.txt</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Acidic Fibroblast Growth Factor (aFGF), Hair follicle regeneration pathway</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>AAV-aFGF, ClickMNP (bioorthogonal click-engineered microneedle patch), HA-DBCO (dibenzocyclooctyne-modified hyaluronic acid), PLGA-N3 (azide-functionalized poly(lactide-co-glycolide))</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>바이오직교 클릭 반응을 통해 AAV-aFGF를 마이크로니들 패치에 고정화하여 진피 내로 효율적으로 전달하고, 지속적인 aFGF 발현을 유도함으로써 모낭 재생을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>FGF signaling, Hair follicle cycling (anagen phase), Dermal angiogenesis, Fibroblast proliferation</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Dermal fibroblasts, Hair follicle cells, Murine alopecia models</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>단일 ClickMNP 투여가 모낭 재생을 가속화하고 진피 혈관형성을 증진하며 휴지기를 연장하여, 자유로운 AAV-aFGF 및 재조합 aFGF 대조군을 능가하는 성능을 보였다. 반복된 제모 사이클에서 모낭 생존성을 보존하고 정상적인 모낭 구조와 증가된 신생 모낭생성 지표를 유지했다. 전사체 분석 결과 섬유모세포 증식, 혈관형성, 모낭 순환과 관련된 경로의 상향 조절을 확인했다.</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>Hair follicle regeneration indices, Anagen phase duration, De novo folliculogenesis indices, Dermal angiogenesis markers, Fibroblast proliferation markers</t>
+        </is>
+      </c>
+      <c r="K1030" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>41821572_Oxidative Stress and Hormone-Regulated Dermal Papi.txt</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>5α-Reductase, Leptin Receptor, Reactive Oxygen Species, p16/pRb senescence markers</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Finasteride, Cerium oxide nanoparticles, Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>L-LP-Fi/CeNP 나노입자는 렙틴 수용체를 통한 표적화된 전달 시스템으로 피노스테라이드를 통한 DHT 억제와 산화세륨 나노입자를 통한 ROS 제거를 동시에 수행하여 진피유두세포의 노화를 역전시킨다.</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>Androgen signaling, Oxidative stress pathway, Cellular senescence pathway, p16/pRb pathway</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, AGA mouse models</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>개발된 L-LP-Fi/CeNP 나노입자는 진피유두세포에서 p16/pRb 노화 마커를 저하시키고 세포 노화를 역전시켜 모낭 유도 능력을 회복시켰다. 임상 표준 치료제인 미녹시딜과 비교했을 때 동등하거나 일부 측면에서 더 우수한 모발 재생 효능을 AGA 마우스 모델에서 보여주었다.</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>p16, pRb, Dihydrotestosterone, Reactive oxygen species</t>
+        </is>
+      </c>
+      <c r="K1031" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>41823643_Scalp Microbiome Alterations in Androgenetic Alope.txt</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>TLR2, NLRP3, Innate immune pathways</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Ketoconazole</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>두피 마이크로바이옴의 변화, 특히 Cutibacterium acnes와 Malassezia 증가가 지질 대사 변화와 함께 TLR2/NLRP3 매개 선천면역 경로를 활성화하여 염증성 사이토카인 생성을 유도하고, 이로 인해 모낭 줄기세포 아포토시스 및 모낭 소형화를 유발하는 것으로 추정된다.</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>TLR2 signaling, NLRP3 signaling, Innate immune activation, Lipid metabolism</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr"/>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>AGA 환자에서 두피 마이크로바이옴의 특징적인 변화가 관찰되며, 특히 Cutibacterium acnes의 풍부도 증가가 가장 일관된 소견이다. 미생물-지질-면역 상호작용이 모낭 소형화 및 AGA 병인에 기여할 수 있으며, 케토코나졸과 같은 지질 조절 중재 치료의 탐색을 정당화한다.</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>Cutibacterium acnes enrichment, Malassezia abundance, Scalp sebum composition, Triglycerides, Palmitic acid, Pro-inflammatory cytokines</t>
+        </is>
+      </c>
+      <c r="K1032" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1032"/>
+  <dimension ref="A1:L1033"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56416,6 +56416,62 @@
         </is>
       </c>
     </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>41849050_Skin bacteriota ameliorates androgenetic alopecia .txt</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>TLR4, NF-κB, Wnt/β-catenin signaling</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr"/>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>피부 미생물군이 TLR4/NF-κB 신호 경로를 조절하여 피부의 염증 미세환경을 개선하고, Wnt/β-catenin 신호 전달과 성장인자 발현을 회복시킴으로써 안드로겐성 탈모를 완화한다.</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>TLR4/NF-κB signaling, Wnt/β-catenin signaling, Inflammatory cytokine signaling</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>DHT-induced AGA model mice, Dorsal skin tissue</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>항생제 처리로 인한 피부 미생물군 감소는 모발 손실을 악화시켰으나, 항생제 미처리 쥐와의 동거 사육으로 피부 미생물이 복구되면서 모발 성장이 개선되었다. Lactobacillus와 Proteus의 상대적 풍부도가 면역염증 균형에 핵심적인 영향을 미치는 주요 속(genus)으로 확인되었다. 미생물 복구는 TLR4/NF-κB 경로를 조절하여 피부 염증을 감소시키고 모낭 성장을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>β-catenin expression, Wnt5a expression, Vegfa mRNA, Fgfr mRNA, Igf1 mRNA, Lef1 mRNA, TLR4 expression, NF-κB expression, IL-6 levels, IL-17 levels, IL-23 levels, TNFα levels, Lactobacillus abundance, Proteus abundance</t>
+        </is>
+      </c>
+      <c r="K1033" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1033"/>
+  <dimension ref="A1:L1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56472,6 +56472,66 @@
         </is>
       </c>
     </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>41861882_Recombinant Filaggrin-2 microneedles reverse andro.txt</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Filaggrin-2 (FLG2), MAPK/Erk signaling pathway, Mitochondrial function</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Recombinant Filaggrin-2 (rFLG2), rFLG2@HA/MNs (rFLG2 with hyaluronic acid microneedles)</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>DHT에 의해 유도된 FLG2 발현 감소를 회복시킴으로써 DPC의 미토콘드리아 기능을 복원하고, MAPK/Erk 신호전달 경로 활성화를 통해 DHT 유도 손상으로부터 모낭유두세포를 보호한다.</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>MAPK/Erk signaling, Bcl-2/Bax apoptotic pathway, Mitochondrial dysfunction pathway</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells (DPCs), C3H mouse (AGA model)</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>rFLG2@HA/MNs는 AGA 마우스 모델에서 모낭 밀도를 현저히 증가시키고 성장기를 연장시켰으며, DHT로 인한 DPC 손상을 MAPK/Erk 경로 활성화와 미토콘드리아 기능 복원을 통해 완화했다. FLG2는 AGA 병인의 핵심 인자로 확인되었으며, rFLG2는 기존 치료법(미녹시딜, 피나스테리드)의 한계를 극복할 수 있는 치료 가능성을 제시한다.</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>Filaggrin-2 (FLG2) expression, Hair follicle density, Anagen phase duration, DPC viability and mitochondrial function</t>
+        </is>
+      </c>
+      <c r="K1034" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1034"/>
+  <dimension ref="A1:L1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56532,6 +56532,62 @@
         </is>
       </c>
     </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>41864295_Reduced Prostate Cancer Risk in Patients with Andr.txt</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>5-Alpha Reductase Type 1, 5-Alpha Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>5-Alpha Reductase Inhibitors</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>5-알파 환원효소 억제제는 테스토스테론의 디하이드로테스토스테론(DHT)으로의 전환을 차단함으로써 안드로겐 의존적 모발 손실을 억제한다.</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>AR signaling, Androgen metabolism</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Patient cohort (TriNetX real-world data)</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>안드로겐성 탈모증 환자에서 5-알파 환원효소 억제제 사용이 전립선암 위험 감소와 관련이 있음을 실제 임상 데이터를 통해 입증하였다. 이는 5-알파 환원효소 억제제의 장기 사용 안전성을 지지하는 증거를 제공한다.</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr"/>
+      <c r="K1035" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1035"/>
+  <dimension ref="A1:L1036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56588,6 +56588,58 @@
         </is>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>41865985_Post-finasteride syndrome survey of dermatologists.txt</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>5-alpha-reductase</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Finasteride</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>5-알파 환원효소 억제제(5-ARIs)의 중단 후 지속적인 증상이 나타나는 현상으로, 본 연구는 이에 대한 피부과 의사들의 인식을 조사하였다.</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>5-alpha-reductase pathway, Androgen metabolism</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr"/>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>스페인 피부과 의사의 83.3%는 임상 실무에서 PFS를 경험하지 못했으며, 대부분(98.1%)은 PFS가 정신적 기원을 가진다고 평가했다. 성기능 장애가 5-ARIs 사용과 관련이 있을 수 있다고 여겨진 반면, 인지 장애, 불안, 우울증은 대다수에 의해 무관한 것으로 간주되었다.</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr"/>
+      <c r="K1036" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1036"/>
+  <dimension ref="A1:L1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56640,6 +56640,66 @@
         </is>
       </c>
     </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>41874081_Effectiveness and Safety of Topical Finasteride fo.txt</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>5a-Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>Finasteride</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Topical finasteride는 5α-reductase type 2를 억제하여 DHT 생성을 감소시키고, 안드로겐 매개 모낭 위축을 방지함으로써 AGA를 치료한다.</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>Androgen receptor signaling, DHT-mediated hair follicle miniaturization</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Hair follicle cells, Dermal papilla cells</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>52주 추적 조사에서 topical finasteride 0.25%는 두정부와 전측두부 모두에서 유의한 모발 증가를 보였으며, 특히 전측두부에서 더 효과적이었다(+32.3 hairs/cm²). 국소 자극만 6.2%의 환자에서 발생했으며 전신 부작용은 없어 우수한 안전성 프로파일을 보였다.</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>Target area hair count (TAHC), Target area hair width (TAHW), Terminal-to-vellus hair ratio, Male Hair Growth Questionnaire (MHGQ), Physician Global Assessment (PGA)</t>
+        </is>
+      </c>
+      <c r="K1037" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1037"/>
+  <dimension ref="A1:L1038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56700,6 +56700,46 @@
         </is>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>41887578_Adjunctive Approaches for Androgenetic Alopecia A .txt</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr"/>
+      <c r="E1038" t="inlineStr"/>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>염증, 산화스트레스, 미세혈관 장애 등이 모낭 소형화에 기여하며, 보조 치료 전략은 두피 항상성 유지를 통해 AGA를 관리한다.</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr"/>
+      <c r="H1038" t="inlineStr"/>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>영양 보충제, 광 기반 치료, 국소 제제, 생활 방식 수정 등의 보조 중재 중 일부는 적당한 효과를 보이지만 대부분은 불충분한 근거를 가지고 있다. 소규모 샘플 크기, 이질적 방법론, 제한된 장기 안전성 데이터, 불일치하는 결과 측정 등의 중요한 격차가 존재한다. 근거 기반의 개별화된 다중 양식 AGA 치료를 지원하기 위해 고품질의 독립적으로 자금 지원된 무작위 대조 시험과 기계적 연구가 필수적이다.</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr"/>
+      <c r="K1038" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1038"/>
+  <dimension ref="A1:L1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56740,6 +56740,170 @@
         </is>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>41877369_Research Progress on Platelet-Rich Plasma PRP in t.txt</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Platelet-Rich Plasma (PRP), Minoxidil, Finasteride</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>PRP는 성장인자가 풍부한 자가 제제로서 혈관신생 및 Wnt/β-catenin, MAPK, Akt/ERK, Notch 신호경로 활성화를 통해 모낭 재생을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr"/>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>PRP 치료는 특히 미녹시딜, 마이크로니들링 또는 레이저 치료와 병용할 때 모발 밀도, 두께 및 환자 만족도 개선을 시연한다. 보고된 부작용은 국소 통증 또는 홍반과 같은 경미하고 일시적인 것이다. 그러나 원심분리, 활성화 및 전달 프로토콜의 이질성은 연구 간 불일치한 결과를 초래한다.</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr"/>
+      <c r="K1039" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>41909969_Trichoscopic Evaluation of the Effectiveness of To.txt</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Prolyl 4-hydroxylase, Hypoxia-Inducible Factor 1-alpha</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Stemoxydine</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Stemoxydine는 Prolyl 4-hydroxylase의 경쟁적 억제제로 작용하여 Hypoxia-Inducible Factor 1-alpha 신호를 활성화하고 모낭의 telogen 단계를 단축시켜 모발 밀도를 증가시킨다.</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>Hypoxia-Inducible Factor 1-alpha signaling, Hair cycle regulation</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Hair follicle</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>35명의 AGA 환자를 3개월간 국소 Stemoxydine 치료한 결과, 중앙값 80%의 임상적 개선을 관찰했으며, 97.1%의 환자에서 1.5개월 내에 새로운 모발 성장이 나타났다. 디지털 분석에서 모발 밀도(p &lt; 0.001)와 직경(p &lt; 0.001)이 통계적으로 유의하게 증가했으며, 남성이 여성보다 더 유의한 임상적 개선을 보였다(p &lt; 0.001). 부작용은 경미하고 잘 견딜 수 있었으며 가장 흔한 부작용은 홍반(22.9%)이었다.</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>Hair density, Hair diameter, AGA grade</t>
+        </is>
+      </c>
+      <c r="K1040" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>41920277_Characterization and Management of Androgenetic Al.txt</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>5-alpha-reductase, Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Minoxidil, Dutasteride, 5-alpha-reductase inhibitors</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>미녹시딜은 혈관확장 및 모낭 성장 촉진을 통해 탈모를 억제하며, 5-알파-환원효소 억제제는 테스토스테론의 디하이드로테스토스테론 전환을 차단하여 안드로겐 의존성 탈모를 감소시킨다.</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>Androgen signaling, Hair follicle growth</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr"/>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>트랜스젠더 남성에서는 남성화 호르몬치료 후 탈모가 발생하며 순환 안드로겐 억제제가 더 효과적인 반면, 트랜스젠더 여성의 경우 선행 안드로겐 노출을 반영하고 여성화 호르몬치료로 안정화될 수 있다. 경구 미녹시딜은 유리한 효능과 안전성 프로필로 인해 모든 트랜스젠더/젠더다양 개인에서 유망한 치료 선택지로 나타났다.</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr"/>
+      <c r="K1041" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1041"/>
+  <dimension ref="A1:L1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56904,6 +56904,122 @@
         </is>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>41922097_Microneedle-Based Codelivery of Platycladus orient.txt</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Hair follicle stem cells, Oxidative stress pathways, Inflammatory pathways, Angiogenesis</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Minoxidil, Platycladus orientalis-derived extracellular vesicles (PO-EVs)</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Platycladus orientalis 유래 세포외소포(PO-EVs)와 미녹시딜 나노입자를 미세바늘을 통해 국소 전달하여 모낭의 항산화, 항염증, 혈관신생 활성을 증진하고 산화스트레스와 염증을 감소시킴으로써 모낭 줄기세포 활성화 및 증식을 유도한다.</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>Oxidative stress pathway, Inflammatory pathway, Angiogenesis pathway, Hair follicle stem cell proliferation</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Hair follicle stem cells, Mouse model of androgenetic alopecia</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>미세바늘 기반 PO-EVs와 미녹시딜 나노입자의 동시 전달은 마우스 모형에서 휴지기에서 성장기로의 전환을 가속화하고 모발 피복 면적과 굵기를 증가시키며 모낭 형태를 복구했다. 모낭 줄기세포의 활성화와 증식, 모낭주변 산화스트레스 및 염증 감소, 모낭주변 미세혈관 밀도 증가가 관찰되었으며 피부 자극이나 전신 독성은 관찰되지 않았다.</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Hair-covered area, Hair shaft thickness, Follicular morphology, Follicular stem cell proliferation, Perifollicular oxidative stress, Perifollicular inflammation, Microvessel density</t>
+        </is>
+      </c>
+      <c r="K1042" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>41926039_Hair Aging Revisited An Expert Delphi Consensus on.txt</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Melanocyte, Hair follicle stem cells, Fibrosis-related pathways</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>모낭 노화는 색소 손실, 모낭 축소화, 그리고 모발 섬유 품질 저하를 포함한 정량적, 정성적 변화를 특징으로 하며, 줄기세포 고갈, 섬유화, 면역노화가 주요 기전이다.</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>Oxidative stress, Melanocyte depletion signaling, Stem cell exhaustion, Fibrosis pathway, Immunosenescence</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr"/>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>전문가 합의를 통해 모낭 노화는 안드로겐 의존적 및 비의존적 영역 모두에서 발생하는 확산형 모발 가늘어짐을 포함한 정의가 수립되었다. 미녹시딜이 유일하게 전문가 합의를 얻은 약물치료이며, 모낭 노화를 늦추기 위한 다른 신흥 치료법들은 추가 연구가 필요하다. 생활방식 개선과 지원적 모발 관리가 예방적 관리로 널리 지지되었다.</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>Pigment loss markers, Melanocyte depletion, Senescence markers</t>
+        </is>
+      </c>
+      <c r="K1043" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,66 +425,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1043"/>
+  <dimension ref="A1:L1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>파일명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>문서유형</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>연구유형</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>타겟(Target)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>화합물(Compound)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>기전(MoA)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>신호전달경로</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>세포/모델</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>핵심발견</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>바이오마커</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>관련도(1-5)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>처리상태</t>
         </is>
@@ -56243,56 +56255,56 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>41821498_Bioorthogonal Click-Engineered Microneedle Patch E.txt</t>
+          <t>patent_survey_AGA_5AR_inhibitors.txt</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Acidic Fibroblast Growth Factor (aFGF), Hair follicle regeneration pathway</t>
+          <t>5α-Reductase Type 1, 5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t>AAV-aFGF, ClickMNP (bioorthogonal click-engineered microneedle patch), HA-DBCO (dibenzocyclooctyne-modified hyaluronic acid), PLGA-N3 (azide-functionalized poly(lactide-co-glycolide))</t>
+          <t>Finasteride analogs, Dutasteride analogs, Novel 5-ARI compounds (Merck, JW중외제약)</t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t>바이오직교 클릭 반응을 통해 AAV-aFGF를 마이크로니들 패치에 고정화하여 진피 내로 효율적으로 전달하고, 지속적인 aFGF 발현을 유도함으로써 모낭 재생을 촉진한다.</t>
+          <t>5α-환원효소를 억제하여 테스토스테론의 DHT 전환을 차단. Type 1/Type 2 선택적 억제 또는 이중 억제를 통해 두피 내 DHT 수준을 감소시켜 모낭 축소를 방지함.</t>
         </is>
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>FGF signaling, Hair follicle cycling (anagen phase), Dermal angiogenesis, Fibroblast proliferation</t>
+          <t>Androgen signaling, DHT-AR pathway</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>Dermal fibroblasts, Hair follicle cells, Murine alopecia models</t>
+          <t>Dermal papilla cells, Hair follicle organ culture, Stump-tailed macaque</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
         <is>
-          <t>단일 ClickMNP 투여가 모낭 재생을 가속화하고 진피 혈관형성을 증진하며 휴지기를 연장하여, 자유로운 AAV-aFGF 및 재조합 aFGF 대조군을 능가하는 성능을 보였다. 반복된 제모 사이클에서 모낭 생존성을 보존하고 정상적인 모낭 구조와 증가된 신생 모낭생성 지표를 유지했다. 전사체 분석 결과 섬유모세포 증식, 혈관형성, 모낭 순환과 관련된 경로의 상향 조절을 확인했다.</t>
+          <t>바스젠바이오 AGA 특허조사보고서(2026.03) 분석 결과, 167건 유효특허 중 5α-환원효소 억제제 관련 특허가 Merck(27건) 등 다수 출원. 한국진입 등록특허 16건, 심사중 11건 확인.</t>
         </is>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>Hair follicle regeneration indices, Anagen phase duration, De novo folliculogenesis indices, Dermal angiogenesis markers, Fibroblast proliferation markers</t>
+          <t>DHT level, 5α-reductase expression</t>
         </is>
       </c>
       <c r="K1030" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1030" t="inlineStr">
         <is>
@@ -56303,52 +56315,52 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>41821572_Oxidative Stress and Hormone-Regulated Dermal Papi.txt</t>
+          <t>patent_survey_AGA_AR_modulators.txt</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
-          <t>5α-Reductase, Leptin Receptor, Reactive Oxygen Species, p16/pRb senescence markers</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>Finasteride, Cerium oxide nanoparticles, Minoxidil</t>
+          <t>SARMs (Ligand Pharmaceuticals), AR antagonists, AR modulators (Aragon Pharmaceuticals)</t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t>L-LP-Fi/CeNP 나노입자는 렙틴 수용체를 통한 표적화된 전달 시스템으로 피노스테라이드를 통한 DHT 억제와 산화세륨 나노입자를 통한 ROS 제거를 동시에 수행하여 진피유두세포의 노화를 역전시킨다.</t>
+          <t>안드로겐 수용체를 선택적으로 조절하여 두피에서의 DHT 신호를 차단하면서 근육/뼈 등에서의 안드로겐 작용은 유지. 선택적 AR 조절제(SARM)를 통한 조직 특이적 작용.</t>
         </is>
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>Androgen signaling, Oxidative stress pathway, Cellular senescence pathway, p16/pRb pathway</t>
+          <t>AR signaling, Androgen-AR-coactivator complex, AR nuclear translocation</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>Dermal papilla cells, AGA mouse models</t>
+          <t>Dermal papilla cells, Prostate cancer cell lines (LNCaP), AR-reporter assay</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t>개발된 L-LP-Fi/CeNP 나노입자는 진피유두세포에서 p16/pRb 노화 마커를 저하시키고 세포 노화를 역전시켜 모낭 유도 능력을 회복시켰다. 임상 표준 치료제인 미녹시딜과 비교했을 때 동등하거나 일부 측면에서 더 우수한 모발 재생 효능을 AGA 마우스 모델에서 보여주었다.</t>
+          <t>Ligand Pharmaceuticals(5건), Aragon Pharmaceuticals(2건) 등이 SARM 특허 다수 보유. 한국 등록 특허 포함. 조직 선택적 AR 조절로 전신 부작용 최소화 전략.</t>
         </is>
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>p16, pRb, Dihydrotestosterone, Reactive oxygen species</t>
+          <t>AR expression, AR nuclear localization, PSA level</t>
         </is>
       </c>
       <c r="K1031" t="n">
@@ -56363,52 +56375,56 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>41823643_Scalp Microbiome Alterations in Androgenetic Alope.txt</t>
+          <t>patent_survey_AGA_JAK_inhibitors.txt</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
-          <t>TLR2, NLRP3, Innate immune pathways</t>
+          <t>JAK1, JAK2, JAK3, ITK</t>
         </is>
       </c>
       <c r="E1032" t="inlineStr">
         <is>
-          <t>Ketoconazole</t>
+          <t>Substituted pyrrolopyrimidine JAK inhibitors (Aclaris Therapeutics), ITK inhibitors</t>
         </is>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t>두피 마이크로바이옴의 변화, 특히 Cutibacterium acnes와 Malassezia 증가가 지질 대사 변화와 함께 TLR2/NLRP3 매개 선천면역 경로를 활성화하여 염증성 사이토카인 생성을 유도하고, 이로 인해 모낭 줄기세포 아포토시스 및 모낭 소형화를 유발하는 것으로 추정된다.</t>
+          <t>JAK-STAT 신호전달 경로를 억제하여 모낭 면역 특권을 회복시키고, T세포 매개 모낭 공격을 방지. ITK 억제를 통한 T세포 활성 조절로 모발 성장 촉진.</t>
         </is>
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>TLR2 signaling, NLRP3 signaling, Innate immune activation, Lipid metabolism</t>
-        </is>
-      </c>
-      <c r="H1032" t="inlineStr"/>
+          <t>JAK-STAT pathway, T cell signaling, IL-15/IL-2 signaling, IFN-gamma pathway</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>T cells, Dermal papilla cells, C3H/HeJ alopecia areata mouse model</t>
+        </is>
+      </c>
       <c r="I1032" t="inlineStr">
         <is>
-          <t>AGA 환자에서 두피 마이크로바이옴의 특징적인 변화가 관찰되며, 특히 Cutibacterium acnes의 풍부도 증가가 가장 일관된 소견이다. 미생물-지질-면역 상호작용이 모낭 소형화 및 AGA 병인에 기여할 수 있으며, 케토코나졸과 같은 지질 조절 중재 치료의 탐색을 정당화한다.</t>
+          <t>Aclaris Therapeutics(5건)가 JAK/ITK 억제제 AGA 적용 특허 주요 출원인. 피롤로피리미딘계 JAK 억제제 및 ITK 억제제가 한국 등록. 국소 적용 가능한 JAK 억제제 개발 추세.</t>
         </is>
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>Cutibacterium acnes enrichment, Malassezia abundance, Scalp sebum composition, Triglycerides, Palmitic acid, Pro-inflammatory cytokines</t>
+          <t>pSTAT3, JAK activity, T cell infiltration, MHC class I expression</t>
         </is>
       </c>
       <c r="K1032" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1032" t="inlineStr">
         <is>
@@ -56419,52 +56435,56 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>41849050_Skin bacteriota ameliorates androgenetic alopecia .txt</t>
+          <t>patent_survey_AGA_Wnt_activators.txt</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>TLR4, NF-κB, Wnt/β-catenin signaling</t>
-        </is>
-      </c>
-      <c r="E1033" t="inlineStr"/>
+          <t>Wnt/β-catenin, GSK3β, CXXC5-Dvl interaction</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>KY19382, Indirubin derivatives, FK506 derivatives (연세대, 서울대, ㈜몰젠바이오)</t>
+        </is>
+      </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t>피부 미생물군이 TLR4/NF-κB 신호 경로를 조절하여 피부의 염증 미세환경을 개선하고, Wnt/β-catenin 신호 전달과 성장인자 발현을 회복시킴으로써 안드로겐성 탈모를 완화한다.</t>
+          <t>Wnt/β-catenin 신호전달 활성화를 통한 모낭 줄기세포 활성 촉진 및 모발 성장 유도. CXXC5-Dvl 상호작용 차단, GSK3β 억제를 통한 β-catenin 안정화.</t>
         </is>
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>TLR4/NF-κB signaling, Wnt/β-catenin signaling, Inflammatory cytokine signaling</t>
+          <t>Wnt/β-catenin pathway, CXXC5-Dvl-β-catenin axis, GSK3β-APC-Axin destruction complex</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>DHT-induced AGA model mice, Dorsal skin tissue</t>
+          <t>Dermal papilla cells, Hair follicle stem cells, C57BL/6 mouse, Human hair follicle organ culture</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>항생제 처리로 인한 피부 미생물군 감소는 모발 손실을 악화시켰으나, 항생제 미처리 쥐와의 동거 사육으로 피부 미생물이 복구되면서 모발 성장이 개선되었다. Lactobacillus와 Proteus의 상대적 풍부도가 면역염증 균형에 핵심적인 영향을 미치는 주요 속(genus)으로 확인되었다. 미생물 복구는 TLR4/NF-κB 경로를 조절하여 피부 염증을 감소시키고 모낭 성장을 촉진한다.</t>
+          <t>연세대 산학협력단, 서울대, ㈜몰젠바이오 등 한국 기관이 FK506 유도체 및 Wnt 활성화 화합물 특허 다수 보유. 한국 진입 등록 특허 5건.</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>β-catenin expression, Wnt5a expression, Vegfa mRNA, Fgfr mRNA, Igf1 mRNA, Lef1 mRNA, TLR4 expression, NF-κB expression, IL-6 levels, IL-17 levels, IL-23 levels, TNFα levels, Lactobacillus abundance, Proteus abundance</t>
+          <t>β-catenin nuclear accumulation, Wnt target gene expression (Axin2, LEF1), Ki67</t>
         </is>
       </c>
       <c r="K1033" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L1033" t="inlineStr">
         <is>
@@ -56475,56 +56495,56 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>41861882_Recombinant Filaggrin-2 microneedles reverse andro.txt</t>
+          <t>patent_survey_AGA_PDE5_vasodilators.txt</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Preclinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
-          <t>Filaggrin-2 (FLG2), MAPK/Erk signaling pathway, Mitochondrial function</t>
+          <t>PDE5, Nitric Oxide (NO), MPC (Mitochondrial Pyruvate Carrier)</t>
         </is>
       </c>
       <c r="E1034" t="inlineStr">
         <is>
-          <t>Recombinant Filaggrin-2 (rFLG2), rFLG2@HA/MNs (rFLG2 with hyaluronic acid microneedles)</t>
+          <t>PDE5 inhibitors/NO-ester dual agents (연세대/㈜주빅), MPC inhibitors (UC California)</t>
         </is>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t>DHT에 의해 유도된 FLG2 발현 감소를 회복시킴으로써 DPC의 미토콘드리아 기능을 복원하고, MAPK/Erk 신호전달 경로 활성화를 통해 DHT 유도 손상으로부터 모낭유두세포를 보호한다.</t>
+          <t>PDE5 억제 및 NO 방출을 통한 두피 혈류 증가로 모낭에 영양 공급 개선. MPC 저해를 통한 모발 성장 촉진 메커니즘 발견.</t>
         </is>
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>MAPK/Erk signaling, Bcl-2/Bax apoptotic pathway, Mitochondrial dysfunction pathway</t>
+          <t>NO-cGMP pathway, PDE5-cGMP signaling, Mitochondrial pyruvate metabolism</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>Dermal papilla cells (DPCs), C3H mouse (AGA model)</t>
+          <t>Vascular endothelial cells, Dermal papilla cells, Hair follicle organ culture</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t>rFLG2@HA/MNs는 AGA 마우스 모델에서 모낭 밀도를 현저히 증가시키고 성장기를 연장시켰으며, DHT로 인한 DPC 손상을 MAPK/Erk 경로 활성화와 미토콘드리아 기능 복원을 통해 완화했다. FLG2는 AGA 병인의 핵심 인자로 확인되었으며, rFLG2는 기존 치료법(미녹시딜, 피나스테리드)의 한계를 극복할 수 있는 치료 가능성을 제시한다.</t>
+          <t>연세대/㈜주빅의 이중작용 PDE5 억제제/NO-에스터 국소 혈류 증진 특허가 한국, 미국, 일본, 중국, 유럽에서 심사중. UC California의 MPC 저해 발모 촉진 특허 한국 등록.</t>
         </is>
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>Filaggrin-2 (FLG2) expression, Hair follicle density, Anagen phase duration, DPC viability and mitochondrial function</t>
+          <t>cGMP level, NO production, Blood flow (laser Doppler)</t>
         </is>
       </c>
       <c r="K1034" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L1034" t="inlineStr">
         <is>
@@ -56535,50 +56555,54 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>41864295_Reduced Prostate Cancer Risk in Patients with Andr.txt</t>
+          <t>patent_survey_AGA_hormonal_modulators.txt</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Clinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Type 1, 5-Alpha Reductase Type 2</t>
+          <t>Estrogen receptor, Progesterone receptor, DHEA metabolism enzymes</t>
         </is>
       </c>
       <c r="E1035" t="inlineStr">
         <is>
-          <t>5-Alpha Reductase Inhibitors</t>
+          <t>DHEA derivatives, Steroidal hormone modulators (Endorecherche), Galderma compounds</t>
         </is>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t>5-알파 환원효소 억제제는 테스토스테론의 디하이드로테스토스테론(DHT)으로의 전환을 차단함으로써 안드로겐 의존적 모발 손실을 억제한다.</t>
+          <t>성호르몬 대사 효소 조절을 통한 국소적 에스트로겐/안드로겐 균형 조절. DHEA 유도체를 통한 모낭 내 호르몬 환경 개선.</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>AR signaling, Androgen metabolism</t>
+          <t>Estrogen receptor signaling, DHEA-androstenedione-testosterone pathway, Aromatase pathway</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>Patient cohort (TriNetX real-world data)</t>
+          <t>Dermal papilla cells, Sebocytes, Hamster flank organ model</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>안드로겐성 탈모증 환자에서 5-알파 환원효소 억제제 사용이 전립선암 위험 감소와 관련이 있음을 실제 임상 데이터를 통해 입증하였다. 이는 5-알파 환원효소 억제제의 장기 사용 안전성을 지지하는 증거를 제공한다.</t>
-        </is>
-      </c>
-      <c r="J1035" t="inlineStr"/>
+          <t>Endorecherche(캐나다, 7건)가 DHEA 유도체 관련 최다 특허 보유. Galderma R&amp;D(프랑스, 4건), L'Oréal(6건) 등 유럽 화장품/제약사의 호르몬 조절 특허가 다수.</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>DHEA-S level, Estrogen/Androgen ratio, Aromatase activity</t>
+        </is>
+      </c>
       <c r="K1035" t="n">
         <v>4</v>
       </c>
@@ -56591,48 +56615,56 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>41865985_Post-finasteride syndrome survey of dermatologists.txt</t>
+          <t>patent_survey_AGA_growth_factors.txt</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
-          <t>5-alpha-reductase</t>
+          <t>VEGF, FGF, Growth hormone receptor, Imidazole-containing compounds</t>
         </is>
       </c>
       <c r="E1036" t="inlineStr">
         <is>
-          <t>Finasteride</t>
+          <t>Growth factor mimetics, Imidazole-containing cyclic derivatives (Changchun GeneScience), Natural product extracts</t>
         </is>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>5-알파 환원효소 억제제(5-ARIs)의 중단 후 지속적인 증상이 나타나는 현상으로, 본 연구는 이에 대한 피부과 의사들의 인식을 조사하였다.</t>
+          <t>모유두세포 증식 촉진 및 성장인자 발현 유도를 통한 모발 성장 활성화. 이미다졸 함유 고리계 유도체를 통한 모낭 재생.</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>5-alpha-reductase pathway, Androgen metabolism</t>
-        </is>
-      </c>
-      <c r="H1036" t="inlineStr"/>
+          <t>VEGF-VEGFR pathway, FGF-FGFR signaling, PI3K/Akt pathway, MAPK/ERK pathway</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, Hair follicle organ culture, C57BL/6 mouse</t>
+        </is>
+      </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>스페인 피부과 의사의 83.3%는 임상 실무에서 PFS를 경험하지 못했으며, 대부분(98.1%)은 PFS가 정신적 기원을 가진다고 평가했다. 성기능 장애가 5-ARIs 사용과 관련이 있을 수 있다고 여겨진 반면, 인지 장애, 불안, 우울증은 대다수에 의해 무관한 것으로 간주되었다.</t>
-        </is>
-      </c>
-      <c r="J1036" t="inlineStr"/>
+          <t>Changchun GeneScience(중국, 4건)가 이미다졸 유도체 AGA 특허 주요 출원인. JW중외제약의 헤테로사이클 유도체 모유두세포 증식 특허가 미국, 중국, 일본 등 다국가 등록.</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>VEGF expression, FGF-7 level, Cell proliferation markers (Ki67, PCNA)</t>
+        </is>
+      </c>
       <c r="K1036" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L1036" t="inlineStr">
         <is>
@@ -56643,378 +56675,58 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>41874081_Effectiveness and Safety of Topical Finasteride fo.txt</t>
+          <t>patent_survey_AGA_overview_167patents.txt</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Patent Survey</t>
         </is>
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Clinical</t>
+          <t>Patent</t>
         </is>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>5a-Reductase Type 2</t>
+          <t>5α-Reductase, Androgen Receptor, JAK/STAT, Wnt/β-catenin, PDE5, VEGF, Estrogen pathway</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>Finasteride</t>
+          <t>167 patented compounds across 98 applicants from 6 countries (KR, JP, CN, US, EU, Others)</t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t>Topical finasteride는 5α-reductase type 2를 억제하여 DHT 생성을 감소시키고, 안드로겐 매개 모낭 위축을 방지함으로써 AGA를 치료한다.</t>
+          <t>바스젠바이오 AGA 저분자 화합물 특허조사보고서(2026.03). 774건→247건→167건 유효특허 선별. 한국8건, 일본6건, 중국29건, 미국66건, 유럽46건, 기타12건.</t>
         </is>
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>Androgen receptor signaling, DHT-mediated hair follicle miniaturization</t>
+          <t>Multiple pathways: AR signaling, Wnt/β-catenin, JAK-STAT, NO-cGMP, DHEA metabolism, Growth factor signaling</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>Hair follicle cells, Dermal papilla cells</t>
+          <t>Multiple models across 167 patents</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t>52주 추적 조사에서 topical finasteride 0.25%는 두정부와 전측두부 모두에서 유의한 모발 증가를 보였으며, 특히 전측두부에서 더 효과적이었다(+32.3 hairs/cm²). 국소 자극만 6.2%의 환자에서 발생했으며 전신 부작용은 없어 우수한 안전성 프로파일을 보였다.</t>
+          <t>한국 진입 유효특허 27건(등록16건+심사중11건) 상세분석. 주요 출원인: Merck(27), Endorecherche(7), EMBL(8), L'Oréal(6), Aclaris(5). 5AR억제제, AR조절제, JAK억제제, Wnt활성화제 4대 기전이 핵심 특허 카테고리.</t>
         </is>
       </c>
       <c r="J1037" t="inlineStr">
         <is>
-          <t>Target area hair count (TAHC), Target area hair width (TAHW), Terminal-to-vellus hair ratio, Male Hair Growth Questionnaire (MHGQ), Physician Global Assessment (PGA)</t>
+          <t>DHT, AR, β-catenin, pSTAT3, VEGF, cGMP</t>
         </is>
       </c>
       <c r="K1037" t="n">
         <v>5</v>
       </c>
       <c r="L1037" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>41887578_Adjunctive Approaches for Androgenetic Alopecia A .txt</t>
-        </is>
-      </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1038" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1038" t="inlineStr"/>
-      <c r="E1038" t="inlineStr"/>
-      <c r="F1038" t="inlineStr">
-        <is>
-          <t>염증, 산화스트레스, 미세혈관 장애 등이 모낭 소형화에 기여하며, 보조 치료 전략은 두피 항상성 유지를 통해 AGA를 관리한다.</t>
-        </is>
-      </c>
-      <c r="G1038" t="inlineStr"/>
-      <c r="H1038" t="inlineStr"/>
-      <c r="I1038" t="inlineStr">
-        <is>
-          <t>영양 보충제, 광 기반 치료, 국소 제제, 생활 방식 수정 등의 보조 중재 중 일부는 적당한 효과를 보이지만 대부분은 불충분한 근거를 가지고 있다. 소규모 샘플 크기, 이질적 방법론, 제한된 장기 안전성 데이터, 불일치하는 결과 측정 등의 중요한 격차가 존재한다. 근거 기반의 개별화된 다중 양식 AGA 치료를 지원하기 위해 고품질의 독립적으로 자금 지원된 무작위 대조 시험과 기계적 연구가 필수적이다.</t>
-        </is>
-      </c>
-      <c r="J1038" t="inlineStr"/>
-      <c r="K1038" t="n">
-        <v>3</v>
-      </c>
-      <c r="L1038" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>41877369_Research Progress on Platelet-Rich Plasma PRP in t.txt</t>
-        </is>
-      </c>
-      <c r="B1039" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1039" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
-        </is>
-      </c>
-      <c r="E1039" t="inlineStr">
-        <is>
-          <t>Platelet-Rich Plasma (PRP), Minoxidil, Finasteride</t>
-        </is>
-      </c>
-      <c r="F1039" t="inlineStr">
-        <is>
-          <t>PRP는 성장인자가 풍부한 자가 제제로서 혈관신생 및 Wnt/β-catenin, MAPK, Akt/ERK, Notch 신호경로 활성화를 통해 모낭 재생을 촉진한다.</t>
-        </is>
-      </c>
-      <c r="G1039" t="inlineStr">
-        <is>
-          <t>Wnt/β-catenin signaling, MAPK signaling, Akt/ERK signaling, Notch signaling, Angiogenesis</t>
-        </is>
-      </c>
-      <c r="H1039" t="inlineStr"/>
-      <c r="I1039" t="inlineStr">
-        <is>
-          <t>PRP 치료는 특히 미녹시딜, 마이크로니들링 또는 레이저 치료와 병용할 때 모발 밀도, 두께 및 환자 만족도 개선을 시연한다. 보고된 부작용은 국소 통증 또는 홍반과 같은 경미하고 일시적인 것이다. 그러나 원심분리, 활성화 및 전달 프로토콜의 이질성은 연구 간 불일치한 결과를 초래한다.</t>
-        </is>
-      </c>
-      <c r="J1039" t="inlineStr"/>
-      <c r="K1039" t="n">
-        <v>4</v>
-      </c>
-      <c r="L1039" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>41909969_Trichoscopic Evaluation of the Effectiveness of To.txt</t>
-        </is>
-      </c>
-      <c r="B1040" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="C1040" t="inlineStr">
-        <is>
-          <t>Clinical</t>
-        </is>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>Prolyl 4-hydroxylase, Hypoxia-Inducible Factor 1-alpha</t>
-        </is>
-      </c>
-      <c r="E1040" t="inlineStr">
-        <is>
-          <t>Stemoxydine</t>
-        </is>
-      </c>
-      <c r="F1040" t="inlineStr">
-        <is>
-          <t>Stemoxydine는 Prolyl 4-hydroxylase의 경쟁적 억제제로 작용하여 Hypoxia-Inducible Factor 1-alpha 신호를 활성화하고 모낭의 telogen 단계를 단축시켜 모발 밀도를 증가시킨다.</t>
-        </is>
-      </c>
-      <c r="G1040" t="inlineStr">
-        <is>
-          <t>Hypoxia-Inducible Factor 1-alpha signaling, Hair cycle regulation</t>
-        </is>
-      </c>
-      <c r="H1040" t="inlineStr">
-        <is>
-          <t>Hair follicle</t>
-        </is>
-      </c>
-      <c r="I1040" t="inlineStr">
-        <is>
-          <t>35명의 AGA 환자를 3개월간 국소 Stemoxydine 치료한 결과, 중앙값 80%의 임상적 개선을 관찰했으며, 97.1%의 환자에서 1.5개월 내에 새로운 모발 성장이 나타났다. 디지털 분석에서 모발 밀도(p &lt; 0.001)와 직경(p &lt; 0.001)이 통계적으로 유의하게 증가했으며, 남성이 여성보다 더 유의한 임상적 개선을 보였다(p &lt; 0.001). 부작용은 경미하고 잘 견딜 수 있었으며 가장 흔한 부작용은 홍반(22.9%)이었다.</t>
-        </is>
-      </c>
-      <c r="J1040" t="inlineStr">
-        <is>
-          <t>Hair density, Hair diameter, AGA grade</t>
-        </is>
-      </c>
-      <c r="K1040" t="n">
-        <v>5</v>
-      </c>
-      <c r="L1040" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>41920277_Characterization and Management of Androgenetic Al.txt</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1041" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>5-alpha-reductase, Androgen Receptor</t>
-        </is>
-      </c>
-      <c r="E1041" t="inlineStr">
-        <is>
-          <t>Minoxidil, Dutasteride, 5-alpha-reductase inhibitors</t>
-        </is>
-      </c>
-      <c r="F1041" t="inlineStr">
-        <is>
-          <t>미녹시딜은 혈관확장 및 모낭 성장 촉진을 통해 탈모를 억제하며, 5-알파-환원효소 억제제는 테스토스테론의 디하이드로테스토스테론 전환을 차단하여 안드로겐 의존성 탈모를 감소시킨다.</t>
-        </is>
-      </c>
-      <c r="G1041" t="inlineStr">
-        <is>
-          <t>Androgen signaling, Hair follicle growth</t>
-        </is>
-      </c>
-      <c r="H1041" t="inlineStr"/>
-      <c r="I1041" t="inlineStr">
-        <is>
-          <t>트랜스젠더 남성에서는 남성화 호르몬치료 후 탈모가 발생하며 순환 안드로겐 억제제가 더 효과적인 반면, 트랜스젠더 여성의 경우 선행 안드로겐 노출을 반영하고 여성화 호르몬치료로 안정화될 수 있다. 경구 미녹시딜은 유리한 효능과 안전성 프로필로 인해 모든 트랜스젠더/젠더다양 개인에서 유망한 치료 선택지로 나타났다.</t>
-        </is>
-      </c>
-      <c r="J1041" t="inlineStr"/>
-      <c r="K1041" t="n">
-        <v>3</v>
-      </c>
-      <c r="L1041" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>41922097_Microneedle-Based Codelivery of Platycladus orient.txt</t>
-        </is>
-      </c>
-      <c r="B1042" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="C1042" t="inlineStr">
-        <is>
-          <t>Preclinical</t>
-        </is>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>Hair follicle stem cells, Oxidative stress pathways, Inflammatory pathways, Angiogenesis</t>
-        </is>
-      </c>
-      <c r="E1042" t="inlineStr">
-        <is>
-          <t>Minoxidil, Platycladus orientalis-derived extracellular vesicles (PO-EVs)</t>
-        </is>
-      </c>
-      <c r="F1042" t="inlineStr">
-        <is>
-          <t>Platycladus orientalis 유래 세포외소포(PO-EVs)와 미녹시딜 나노입자를 미세바늘을 통해 국소 전달하여 모낭의 항산화, 항염증, 혈관신생 활성을 증진하고 산화스트레스와 염증을 감소시킴으로써 모낭 줄기세포 활성화 및 증식을 유도한다.</t>
-        </is>
-      </c>
-      <c r="G1042" t="inlineStr">
-        <is>
-          <t>Oxidative stress pathway, Inflammatory pathway, Angiogenesis pathway, Hair follicle stem cell proliferation</t>
-        </is>
-      </c>
-      <c r="H1042" t="inlineStr">
-        <is>
-          <t>Hair follicle stem cells, Mouse model of androgenetic alopecia</t>
-        </is>
-      </c>
-      <c r="I1042" t="inlineStr">
-        <is>
-          <t>미세바늘 기반 PO-EVs와 미녹시딜 나노입자의 동시 전달은 마우스 모형에서 휴지기에서 성장기로의 전환을 가속화하고 모발 피복 면적과 굵기를 증가시키며 모낭 형태를 복구했다. 모낭 줄기세포의 활성화와 증식, 모낭주변 산화스트레스 및 염증 감소, 모낭주변 미세혈관 밀도 증가가 관찰되었으며 피부 자극이나 전신 독성은 관찰되지 않았다.</t>
-        </is>
-      </c>
-      <c r="J1042" t="inlineStr">
-        <is>
-          <t>Hair-covered area, Hair shaft thickness, Follicular morphology, Follicular stem cell proliferation, Perifollicular oxidative stress, Perifollicular inflammation, Microvessel density</t>
-        </is>
-      </c>
-      <c r="K1042" t="n">
-        <v>5</v>
-      </c>
-      <c r="L1042" t="inlineStr">
-        <is>
-          <t>성공</t>
-        </is>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>41926039_Hair Aging Revisited An Expert Delphi Consensus on.txt</t>
-        </is>
-      </c>
-      <c r="B1043" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="C1043" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>Melanocyte, Hair follicle stem cells, Fibrosis-related pathways</t>
-        </is>
-      </c>
-      <c r="E1043" t="inlineStr">
-        <is>
-          <t>Minoxidil</t>
-        </is>
-      </c>
-      <c r="F1043" t="inlineStr">
-        <is>
-          <t>모낭 노화는 색소 손실, 모낭 축소화, 그리고 모발 섬유 품질 저하를 포함한 정량적, 정성적 변화를 특징으로 하며, 줄기세포 고갈, 섬유화, 면역노화가 주요 기전이다.</t>
-        </is>
-      </c>
-      <c r="G1043" t="inlineStr">
-        <is>
-          <t>Oxidative stress, Melanocyte depletion signaling, Stem cell exhaustion, Fibrosis pathway, Immunosenescence</t>
-        </is>
-      </c>
-      <c r="H1043" t="inlineStr"/>
-      <c r="I1043" t="inlineStr">
-        <is>
-          <t>전문가 합의를 통해 모낭 노화는 안드로겐 의존적 및 비의존적 영역 모두에서 발생하는 확산형 모발 가늘어짐을 포함한 정의가 수립되었다. 미녹시딜이 유일하게 전문가 합의를 얻은 약물치료이며, 모낭 노화를 늦추기 위한 다른 신흥 치료법들은 추가 연구가 필요하다. 생활방식 개선과 지원적 모발 관리가 예방적 관리로 널리 지지되었다.</t>
-        </is>
-      </c>
-      <c r="J1043" t="inlineStr">
-        <is>
-          <t>Pigment loss markers, Melanocyte depletion, Senescence markers</t>
-        </is>
-      </c>
-      <c r="K1043" t="n">
-        <v>3</v>
-      </c>
-      <c r="L1043" t="inlineStr">
         <is>
           <t>성공</t>
         </is>

--- a/AGA_data.xlsx
+++ b/AGA_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1037"/>
+  <dimension ref="A1:L1059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>파일명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>문서유형</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>연구유형</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>타겟(Target)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>화합물(Compound)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>기전(MoA)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>신호전달경로</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>세포/모델</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>핵심발견</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>바이오마커</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>관련도(1-5)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>처리상태</t>
         </is>
@@ -56732,6 +56720,1234 @@
         </is>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>5-알파 환원 효소억제제를 함유하는 안드로겐성탈모증 치료용 약제학적 조성물.txt</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>5-Alpha Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Finasteride, 17β-(N-t-butylcarbamoyl)-4-aza-5α-androst-1-en-3-one</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>5α-환원효소 2 억제제를 투여하여 두피에서 DHT(5α-디하이드로테스토스테론) 수준을 저하시킴으로써 안드로겐성 탈모증을 치료하고 모발 성장을 촉진시킨다.</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>Androgen signaling, DHT biosynthesis</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr"/>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>5α-환원효소 2 억제제(피나스테라이드 등)를 5㎎/일 이하의 용량으로 투여하여 안드로겐성 탈모증(남성형 대머리)을 치료 및 억제할 수 있다. 경구 투여 및 국소 투여 모두 가능하며, 특히 0.05~1.0㎎/일의 저용량 투여가 효과적이다.</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>DHT (5α-dihydrotestosterone), Hair growth</t>
+        </is>
+      </c>
+      <c r="K1038" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Composition for preventing or treating of benign prostatic hyperplasia or alopecia comprising extracts of Salvia miltiorrhiza Bunge as an effective ingredient 22년 버전.txt</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>5α-Reductase Type 2 (5AR2), Androgen Receptor (AR), Prostate-Specific Antigen (PSA), Steroid Receptor Coactivator-1 (SRC-1), NQO1</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Salvia miltiorrhiza Bunge extract, Tanshinone 1, Tanshinone 2a, Cryptotanshinone, 15,16-Dihydrotanshinone, Tanshinoic acid, Salvianolic acid B, Finasteride, Saw palmetto extract, Testosterone, Dihydrotestosterone (DHT)</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>단삼 추출물의 주요 탄시논 성분은 NAD+ 촉진제로서 NQO1 효소를 표적으로 하며, 세포 내 NAD+ 농도를 증가시켜 Sirtuin, AMPK, PGC-1α를 활성화함으로써 항노화 효과 및 대사질환 개선을 통해 5α-환원효소, 안드로겐 수용체, PSA의 발현을 억제하여 전립선비대증 및 탈모증을 개선한다.</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Androgen signaling, DHT-AR pathway, NAD+/Sirtuin pathway, AMPK pathway, PGC-1α mitochondrial biogenesis, Cell cycle regulation (G1/S, Cyclin D1), Apoptosis regulation (Bcl-2)</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>Prostate tissue (rat), Sprague-Dawley rat model, Prostate epithelial cells, Prostate stromal cells</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>40-99% 에탄올 추출한 단삼 추출물(T40, T70)은 테스토스테론으로 유도한 전립선비대증 동물 모델에서 5AR2, AR, PSA 단백질 발현을 현저히 억제하였으며, 피나스테라이드와 거의 동일한 수준의 전립선 무게 감소 효과를 나타냈다. 특히 고에탄올 농도 추출물은 탄시논류 함량이 높고 살비아놀릭산 B 함량이 낮아 부작용 없이 효과적인 것으로 확인되었다.</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>DHT, 5α-Reductase Type 2, Androgen Receptor, PSA (Prostate-Specific Antigen), PCNA (Proliferating Cell Nuclear Antigen), Cyclin D1, Bcl-2, Salvianolic acid B, Tanshinone components, NAD+, Prostate weight/index</t>
+        </is>
+      </c>
+      <c r="K1039" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>HALOGENATED SELECTIVE ANDROGEN RECEPTOR MODULATORS AND METHODS OF USE THEREOF 07년도.txt</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Androgen Receptor (AR), Selective Androgen Receptor Modulator (SARM)</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Compound 1, Compound 2, Compound 3, Compound 4, Compound 5, Compound 6, Compound 21, Compound 22, Compound 23, Testosterone, Dihydrotestosterone (DHT), Testosterone Enanthate, Testosterone Propionate (TP), MENT (7-Methyl-Nortestosterone), Cyproterone Acetate</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>선택적 안드로겐 수용체 모듈레이터(SARM)는 비스테로이드계 리간드로서 안드로겐 수용체에 선택적으로 결합하여 안드로겐 활성 또는 항안드로겐 활성을 나타내며, 기존 테스토스테론 기반 치료법의 부작용을 최소화하면서 조직 특이적 안드로겐 반응을 유도한다.</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>Androgen Receptor Signaling, Hypothalamic-Pituitary-Gonadal (HPG) Axis, Gonadotropin Suppression, Bone Remodeling, Muscle Protein Synthesis/Catabolism</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Rat model (Sprague-Dawley or similar), Castrated rats, Intact rats, Androgen-responsive tissues (prostate, seminal vesicles, levator ani muscle)</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>본 발명의 SARM 화합물들은 래트 모델에서 용량 의존적인 안드로겐 및 동화작용 활성을 나타내었으며, 전립선, 정낭, 항문 기근 등 안드로겐 반응성 조직의 무게를 회복시켰다. 특히 화합물 1-6은 남성 피임, ADAM/ADIF 관련 증상 치료, 근육소모증 예방, 골다공증 치료 등에 유용하며, 기존의 테스토스테론 에스테르 기반 치료법의 한계를 극복할 수 있는 선택적 조직 타겟팅 특성을 갖춘다.</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>LH (Luteinizing Hormone) levels, FSH (Follicle Stimulating Hormone) levels, Androgen-responsive tissue weight (prostate, seminal vesicles, levator ani muscle), Testosterone levels, DHT (Dihydrotestosterone) levels, Spermatogenesis markers (azoospermia, oligospermia)</t>
+        </is>
+      </c>
+      <c r="K1040" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>HALOGENATED SELECTIVE ANDROGEN RECEPTOR MODULATORS AND METHODS OF USE THEREOF 12년도.txt</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Androgen Receptor, 5-alpha Reductase</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Selective Androgen Receptor Modulators (SARMs), Halogenated SARM compounds, Compound 21 (S-147), Testosterone, DHT (Dihydrotestosterone)</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>선택적 안드로겐 수용체 모듈레이터(SARM)는 안드로겐 수용체에 결합하여 조직-특이적 안드로겐 활성 또는 항안드로겐 활성을 나타낸다. 이는 기존의 5-알파 리덕테이즈 억제제(피나스테라이드, 두타스테라이드)와 달리 조직 선택성을 통해 원하는 안드로겐 효과는 유지하면서 부작용을 최소화할 수 있다.</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>Androgen Receptor signaling, DHT synthesis pathway, Bone metabolism, Muscle protein synthesis</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr"/>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>할로겐화된 선택적 안드로겐 수용체 모듈레이터(SARM) 화합물들이 안드로겐 감소 관련 증상 치료에 유용함을 제시한다. SARM은 남성 피임, ADAM(나이든 남성에서 안드로겐 감소) 및 ADIF(여성에서 안드로겐 감소) 관련 증상 치료, 발기부전, 성욕감소, 골다공증, 근육소모증 등의 치료에 활용 가능하다. 특히 비스테로이드 안드로겐의 초기 보고로서 기존 스테로이드 호르몬제의 한계를 극복할 수 있는 잠재력을 가진다.</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>Testosterone, DHT (Dihydrotestosterone), Serum androgen levels</t>
+        </is>
+      </c>
+      <c r="K1041" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>HALOGENATED SELECTIVE ANDROGEN RECEPTOR MODULATORS ANDMETHODS OF US THEREOF 11년도 9월.txt</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Androgen Receptor, 5-alpha Reductase</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Compound 1, Compound 2, Compound 3, Compound 4, Compound 5, Compound 6, Compound 21, Testosterone Propionate, Halogenated Selective Androgen Receptor Modulators</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>선택적 안드로겐 수용체 모듈레이터(SARM)는 안드로겐 수용체에 조직-특이적으로 결합하여 일부 화합물은 예기치 않은 안드로겐 및 동화 활성을 나타내고, 다른 화합물은 항안드로겐 활성을 나타낸다. 이는 기존의 5-알파 리덕테이즈 억제제의 성적 기능 부작용을 회피하면서 선택적 조직 작용을 제공한다.</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>Androgen Receptor signaling, Hypothalamic-Pituitary-Gonadal axis, Spermatogenesis regulation</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Rat models, Prostate tissue, Seminal vesicle tissue, Bulbocavernosus muscle</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>할로겐화된 SARM 화합물들은 거세된 래트에서 용량-의존적인 안드로겐 및 동화 활성을 보였다. 화합물 1과 화합물 21은 LH 및 FSH 수준에 영향을 미쳤으며, 이들은 남성 피임, 성적 장애, 골다공증, 근육소모증 및 전립선암 치료 등 다양한 호르몬 관련 증상의 치료에 유용할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>Prostate weight, Seminal vesicle weight, Bulbocavernosus muscle weight, LH (Luteinizing Hormone), FSH (Follicle Stimulating Hormone), Testosterone levels</t>
+        </is>
+      </c>
+      <c r="K1042" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Pharmaceutical composition for alleviating or treating alopecia via improvement of inflammation and expression inhibition of 5α reductase in human dermal papilla cell and surrounding cells thereof 21년도.txt</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>5α-Reductase, IL-6, TNF-α, COX-2, iNOS, 5-Lipoxygenase (5-LO), Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Genistein, Kaempferol, EGCG (Epigallocatechin gallate), Finasteride, Testosterone, DHT (Dihydrotestosterone), Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>안드로겐 호르몬(테스토스테론, DHT)에 의해 유도되는 모유두 세포의 염증 반응 억제 및 5α-환원효소의 발현 억제를 통해 탈모를 개선한다. 제니스테인과 캠페롤은 IL-6, TNF-α 등의 전염증 사이토카인 생성을 억제하고, 항산화 작용으로 활성산소를 제거하여 모낭 염증을 개선한다.</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>Androgen signaling, IL-6/TNF-α inflammatory pathway, COX-2/Prostaglandin pathway, NO/iNOS pathway, 5-Lipoxygenase/Leukotriene pathway, Oxidative stress/ROS pathway</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>Human dermal papilla cells (hDPC), Macrophage cell line (THP-1), Mast cells, Keratinocytes, C57BL/6 female mice, Matrix cells</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>제니스테인과 캠페롤의 조합은 안드로겐 유도 탈모 모델에서 피나스테라이드와 유사하거나 우수한 모발 재생 효과를 보였다. 8주간의 임상시험에서 피험자의 모발 수가 평균 21.0% 증가하고 모발 굵기가 29.5% 증가하였으며, 성적 부작용 없이 안전한 탈모 치료 효과를 나타냈다.</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>DHT, IL-6, TNF-α, COX-2, iNOS, 5-Lipoxygenase, Hair count (개/㎠), Hair thickness (㎜), Hair weight</t>
+        </is>
+      </c>
+      <c r="K1043" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>patent_1.txt</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>5-alpha reductase Type 1, 5-alpha reductase Type 2, Androgen Receptor, JAK1, JAK2, NK-1 receptor, NK-3 receptor, CB1 receptor, PDE5</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Finasteride, Dutasteride, JAK inhibitors, Androgen receptor modulators, NK-3 receptor antagonists, Imidazolidine derivatives, Triazaazole derivatives, Quinoline carboxylic acid compounds, Oxazolone compounds, Phenyl-pyrazolo[3,4-b]pyridine-4-carboxylic acid derivatives, Purine compounds, FK506 derivatives, Indoline derivatives</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>남성형 탈모 치료를 위한 저분자 화합물들의 작용 기전은 5α-리덕타제 억제, 안드로겐 수용체 조절/분해, JAK 억제, NK 수용체 길항 등 다양한 경로를 포함한다. 이 중 일부는 국소 혈류 증진을 통한 경피 투약 형태로도 개발되고 있다.</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>Androgen signaling, JAK/STAT pathway, NK receptor signaling, CB1 receptor signaling, NO/cGMP pathway</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr"/>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>한국, 일본, 중국, 미국, 유럽 5개국에서 총 774건의 남성형 탈모 치료용 저분자 화합물 관련 특허가 검색되었으며, 효능 실험 결과를 포함한 유효특허 167건을 최종 선별하였다. 현재 권리가 유효한 특허는 JAK 억제제, 안드로겐 수용체 조절제, NK 수용체 길항제 등 다양한 기전을 포함하고 있으며, 한국에 진입한 27건의 특허에 대해 상세 분석을 수행하였다.</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>DHT, 5-alpha reductase activity</t>
+        </is>
+      </c>
+      <c r="K1044" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>생약으로부터 발모 촉진 성분의 추출 방법 및 그 추출물.txt</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Patent</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr"/>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Bupleurum Radix (시호), Rubia akane Radix (천초), Angelica gigantis Radix (당귀), Mori Folium (상엽), Cnidi Rhizoma (천궁), Corni Fructus (산수유)</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>전통 생약 성분들을 검은깨 기름 또는 정제수로 침출하여 추출한 생약 혼합물이 탈모증 치료 효과를 발휘하는 것으로 보이나, 구체적인 분자 메커니즘은 명시되지 않음.</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr"/>
+      <c r="H1045" t="inlineStr"/>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>6가지 한의학 생약의 혼합 추출물을 300명의 탈모 환자에게 90일 이상 적용한 결과, 약 90%에서 탈모 중지, 약 70%에서 발모가 확인되었음. 본 추출물은 장년성 탈모증, 여성 탈모증, 원형 탈모증에 효과적이며 장기간 사용 시 부작용이 없는 것으로 보고됨.</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr"/>
+      <c r="K1045" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>10098703_Minoxidil increases 17 beta-hydroxysteroid dehydro.txt</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>5-Alpha Reductase Type 1, 5-Alpha Reductase Type 2, Androgen Receptor, TGF-beta1, TGF-beta2, DKK-1, IL-6</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>테스토스테론이 5α 리덕타아제에 의해 DHT로 전환되고, DHT가 안드로겐 수용체(AR)와 결합하여 이량체를 형성한 후 핵으로 진입하여 TGF-β1, TGF-β2, DKK-1, IL-6 등의 안드로겐 표적 유전자 발현을 유도함으로써 모낭의 소형화를 촉진한다.</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>Androgen Receptor signaling, TGF-beta signaling, Wnt/beta-catenin signaling, Developmental patterning pathways</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, Hair follicle dermal sheath, Hair follicle epithelium, Hair follicle stem cells, Dermal fibroblasts</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>남성형 탈모(MPHL)는 전두부 및 정점 모낭의 선택적 소형화로 특징지어지며, 이는 개발 기원과 관련된 피부 영역 간 생물학적 차이에 의해 설명될 수 있다. 5α 리덕타아제 II는 더마 유두에서만 발현되고, 안드로겐 수용체는 모낭 더마에서만 발현되어 국소적 패턴 형성을 결정한다. AR 유전자좌(Xq11-12)와 20p11 유전자좌가 MPHL과 강한 연관성을 보이며, 미니어처화된 모낭은 더마 유두의 크기 감소와 근립모근의 지방 조직으로의 교체를 특징으로 한다.</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>DHT, AR expression, TGF-beta1, TGF-beta2, DKK-1, IL-6, p16INK4a</t>
+        </is>
+      </c>
+      <c r="K1046" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>10230220_Androgenetic alopecia finasteride treated hair los.txt</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>In vitro</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>5α-Reductase Type I, 5α-Reductase Type II, 5β-Reductase</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Finasteride, Epristeride, Hybrid compound 3, Compound 12, Compound 13</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>신규 하이브리드 화합물 3은 피나스테리드의 A 고리를 에프리스테리드의 D 고리 위치에 치환하여 설계되었으며, 피나스테리드와 유사한 경쟁적 기전으로 5α-리덕타제를 억제한다. IC50 값 71 nM으로 피나스테리드(35 nM)보다 약간 낮지만, 에프리스테리드의 주요 약리학적 골격을 유지하면서 우수한 억제 활성을 나타낸다.</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>Androgen signaling, Testosterone to DHT conversion</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>Human prostate tissue homogenate from benign prostatic hyperplasia patients</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>신규 하이브리드 화합물 3은 IC50 71 nM의 5α-리덕타제 억제 활성을 보였으며, 이는 피나스테리드의 경쟁적 억제 기전을 유지하면서도 에프리스테리드의 골격을 결합한 구조이다. 분자 도킹 연구 결과, 하이브리드 화합물은 피나스테리드와 유사한 활성 부위 상호작용을 보이며, 에프리스테리드보다 우수한 결합 친화성을 나타낸다. A 고리의 페닐 치환(화합물 12, 13)은 5α-리덕타제 억제 활성을 현저히 감소시켰다.</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>DHT, Testosterone, IC50</t>
+        </is>
+      </c>
+      <c r="K1047" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>10344067_Androgenetic alopecia in men the scale of the prob.txt</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>5-alpha Reductase, Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Finasteride, Dutasteride, Minoxidil, Rosemary oil, Melatonin, Watercress, Procyanidin, Marine complex, Serenoa repens</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>파이나스테라이드와 두타스테라이드는 5-알파 리덕타아제 억제제로서 안드로겐 의존적 탈모를 억제하며, 미녹시딜은 안드로겐 대사와 무관하게 모낭 성장을 촉진한다. 대체 치료제들은 다양한 메커니즘을 통해 모발 밀도 증가를 유도한다.</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>Androgen metabolism, Hair follicle miniaturization</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr"/>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>네트워크 메타분석 결과 경구 두타스테라이드, 국소/경구 미녹시딜, 경구/국소 파이나스테라이드가 남성형 탈모 치료에 효과적임을 확인했다. 토피컬 멜라토닌과 로즈마리 오일 같은 일부 대체 약물들이 기존 치료제와 비교했을 때 유사한 효능을 보였다.</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>Total hair density (hairs/cm²)</t>
+        </is>
+      </c>
+      <c r="K1048" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>10352926_Antiandrogen treatment of polycystic ovary syndrom.txt</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr"/>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Levothyroxine, Meropenem, Hydrocortisone</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr"/>
+      <c r="H1049" t="inlineStr"/>
+      <c r="I1049" t="inlineStr"/>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>TSH, FT4, FT3</t>
+        </is>
+      </c>
+      <c r="K1049" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>10369534_Androgenetic alopecia.txt</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>5α-Reductase Type II, 3α-Hydroxysteroid Dehydrogenase, Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Cell-free fat extract (CEFFE), Finasteride, Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>CEFFE는 DHT/AR 신호전달 경로를 조절하고 지역적 혈관신생을 촉진함으로써 AGA를 치료한다. CEFFE는 모낭 세포의 증식을 촉진하고, DHT로 인한 세포주기 정지를 완화하며, 세포 사멸을 억제하고, 세포내 DHT 농도를 감소시키며, AR 발현을 하향조절한다.</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>DHT/AR signaling, Angiogenesis pathway, Cell proliferation, Cell cycle regulation</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells (DPCs), C57BL/6 mice, Adipose-derived stem cells (ADSCs)</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>CEFFE 처리된 쥐에서 휴지기 진입율과 모발 피복 백분율이 증가했으며, CD31 양성 모세혈관과 Ki67 양성 세포의 수가 증가했다. CEFFE는 DHT 유도 AGA 모델에서 모낭 밀도와 모발 성장율을 증가시키는 안전하고 효과적인 치료 옵션이다.</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>DHT, CD31, Ki67, Androgen receptor (AR), 5α-Reductase Type II, 3α-Hydroxysteroid Dehydrogenase</t>
+        </is>
+      </c>
+      <c r="K1050" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>10439233_Efficacy of finasteride 1 mg in the treatment of a.txt</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>5a-Reductase Type II</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Finasteride, Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Finasteride는 5a-Reductase Type II 효소를 억제하여 테스토스테론의 DHT(디하이드로테스토스테론)로의 전환을 차단함으로써 모낭의 미니어처화를 방지하고 모발 성장을 유지한다.</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>Androgen signaling, DHT-AR pathway</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr"/>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>이탈리아 피부과의사 1,153명을 대상으로 한 설문조사 결과, 91%의 의사가 피나스테리드를 AGA의 가장 효과적인 경구 치료제로 평가했다. 그러나 69%의 음의 응답이 성기능 부작용(발기부전, 성욕감소, 사정 문제)과 심리적 부작용으로 인한 것으로 나타났다. 장기(5년) 치료를 권장하는 의사는 33%였다.</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>DHT, Loss of libido, Erectile dysfunction, Ejaculation problems</t>
+        </is>
+      </c>
+      <c r="K1051" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>10461639_Management of androgenetic alopecia.txt</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Androgen Receptor, 5-alpha reductase Type 1, 5-alpha reductase Type 2, Estrogen receptor, Aromatase</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>Finasteride, Minoxidil, Testosterone, Dihydrotestosterone, Tretinoin, R1881</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>안드로겐이 유전적으로 감수성 있는 모낭의 상피세포에 작용하여 모낭 축소화를 유발하며, 이는 5α-환원효소에 의한 테스토스테론의 DHT로의 전환과 진피유두세포에서의 TGF-β1 분비를 통해 매개된다.</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>Androgen receptor signaling, TGF-beta signaling, IGF-1 signaling, Wnt/beta-catenin, Hair follicle cycling, Androgen metabolism</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, Keratinocytes, Hair follicle epithelial cells, Sebaceous glands, Sweat glands</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>안드로겐의존적 탈모는 다유전자 성질을 가지며, X-염색체의 AR/EDA2R 유전자좌와 20번 염색체 11p 유전자좌가 주요 위험 유전자이다. 진피유두세포에서의 안드로겐 수용체 발현 증가와 TGF-β1 생성이 두피 모낭의 축소화를 매개하는 핵심 메커니즘으로 밝혀졌다.</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>DHT, Testosterone, Androgen receptor expression, TGF-beta1, IGF-1, 5-alpha reductase activity</t>
+        </is>
+      </c>
+      <c r="K1052" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>10469326_The mRNA for protease nexin-1 is expressed in huma.txt</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>5-alpha reductase Type 2, Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>Finasteride, Minoxidil, EGCG, Ginseng, Plant extracts</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>본 체계적 문헌고찰은 AGA의 병인 및 병태생리 규명을 위해 사용된 다양한 실험실 모델들을 검토하였으며, 특히 5-알파 리덕타제 억제 및 DHT 효과에 초점을 맞춤. 현재 승인된 약물(미녹시딜, 피나스테리드)의 개발에 기여한 in vitro, in vivo 및 ex vivo 모델들의 한계점을 분석하고 더 생리적으로 관련성 높은 3D 오르가노이드 모델의 필요성을 강조함.</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>Androgen signaling, DHT synthesis and metabolism</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Dermal papilla cells, Immortalized cell lines, Mouse models, Rat models, Stump-tailed macaque, Human scalp tissue explants, Human skin tissue</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>총 101개의 AGA 관련 연구를 분석한 결과, 70개(69%)의 연구는 2D 단일층 세포 모델을 사용하였으며 27개(27%)는 마우스/원숭이 등 in vivo 모델을 사용함. 3D 오르가노이드 또는 오르가노타입 인간 피부 배양 모델을 사용한 연구는 전무하였음. 저자들은 환자 유래 3D 조직 모델이 현재의 동물 모델 및 2D 세포 배양보다 인간 두피 조직에 더 가깝고 새로운 치료법 개발을 촉진할 수 있음을 권장함.</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>DHT, 5-alpha reductase activity, Androgen receptor expression, Hair growth</t>
+        </is>
+      </c>
+      <c r="K1053" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>10495374_The effects of finasteride on scalp skin and serum.txt</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>5α-Reductase, 17,20 desmolase-lyase (CYP17A1), 3β-Hydroxysteroid dehydrogenase (3β-HSD), 3α-Hydroxysteroid dehydrogenase (3α-HSD), 17β-Hydroxysteroid dehydrogenase (17β-HSD), Aromatase, StAR (Steroidogenic acute regulatory protein), CYP11A1 (Cytochrome P450 side chain cleavage)</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Finasteride, Dutasteride, Formestane</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>스테로이드 생성 효소 억제제는 신경활성 스테로이드의 합성과 대사를 조절하여 신경전달물질 시스템의 기능을 조절한다. 특히 5α-환원효소와 17,20 데스몰라제-리아제 억제제는 도파민 항진 관련 행동 장애의 치료 효능을 나타낸다.</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>Steroidogenesis pathway, Dopaminergic signaling, Stress response pathway, Glucocorticoid signaling, Androgen biosynthesis, Neurosteroid synthesis</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>Neurons, Glial cells, CD1 mice</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>스테로이드 생성 경로의 억제제들은 신경정신 장애의 치료에 재목적화될 가능성이 있으며, 특히 5α-환원효소와 17,20 데스몰라제-리아제 억제제가 도파민 항진 관련 행동 장애에 치료 효능을 보인다. 그러나 이러한 약물들의 특이성 부족으로 인한 내분비 부작용에 대한 우려가 제기되며, 뇌 특이성이 높은 스테로이드 생성 조절제의 개발이 정신질환 치료의 새로운 대안이 될 수 있음을 시사한다.</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>DHT (Dihydrotestosterone), Pregnenolone, Progesterone, Marble burying behavior, Motility</t>
+        </is>
+      </c>
+      <c r="K1054" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>10495375_Clinical dose ranging studies with finasteride a t.txt</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>5α-Reductase Type I, 5α-Reductase Type II</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Dutasteride, Finasteride</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>5α-Reductase 억제제는 디하이드로테스토스테론(DHT)으로의 역전환을 억제하여 남성형 탈모증의 주요 원인 호르몬인 DHT 수준을 감소시킨다. Dutasteride는 Type I 및 Type II 5α-Reductase를 모두 억제하는 이중 억제제로서 finasteride보다 더 강력한 DHT 억제 효과를 나타낸다.</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>Androgen signaling, DHT metabolism</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr"/>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>간헐적 dutasteride 치료(주 2회 또는 주 3회)는 24주 후 모발 밀도와 직경을 유의하게 증가시켰으며, 주 3회 투여가 주 2회보다 우수했다. 성기능 부작용은 모든 치료군에서 유사하였고 5-10%의 경미한 성기능 장애만 관찰되었으며, dutasteride의 저용량 간헐적 투여는 finasteride 1mg 일일 투여와 비교하여 안전성과 효능이 우수하지 않았다.</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>DHT, Hair count, Hair diameter</t>
+        </is>
+      </c>
+      <c r="K1055" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>10527763_Androgenetic alopecia in vivo models.txt</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Androgen Receptor, 5-alpha-reductase Type II, Wnt signaling, FGF signaling, BMP signaling, EDA/EDAR signaling, SHH signaling</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>Minoxidil</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>모발 여포의 발달과 재생은 피부 중배엽과 외배엽 유래 세포 간의 신호 전달 교차작용을 통해 조절된다. 특히 남성호르몬 수용체 활성화는 여포 소형화를 유도하고, Wnt, FGF, BMP 등의 신호 경로는 모발 재생과 성장 단계를 조절한다.</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>Androgen Receptor signaling, Wnt/beta-catenin, FGF signaling, BMP signaling, EDA/EDAR signaling, SHH/Notch signaling</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>Hair follicle stem cells, Dermal papilla cells, Dermal fibroblasts, Keratinocytes, Mouse hair follicles, Human hair follicles, T cells</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>모발 여포는 배아 발달 중 상피-중배엽 신호 교차작용을 통해 형성되며, 성인에서는 휴지기, 성장기, 퇴행기, 탈출기의 주기적 사이클을 거친다. 안드로겐성 탈모증은 AR 과활성화와 제2형 5-알파 환원효소 증가로 인한 DHT 수준 증가에 의해 야기되며, 현재 인간 모발 재생 치료법 개발을 위해서는 생체 외 인간 모발 여포 모델의 개선이 필수적이다.</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>DHT, Androgen Receptor expression, Hair cycle phase markers, Hair follicle miniaturization</t>
+        </is>
+      </c>
+      <c r="K1056" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>10534633_Changes in hair weight and hair count in men with .txt</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>5-alpha reductase Type 1, 5-alpha reductase Type 2, Androgen Receptor</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Finasteride, Dutasteride, Minoxidil, Ketoconazole, Sulfotransferase</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>5-알파 환원효소 억제제(피나스테리드, 두타스테리드)는 테스토스테론을 디하이드로테스토스테론(DHT)으로의 변환을 억제하여 모낭의 안드로겐 수용체 신호를 감소시킨다. 미녹시딜은 혈관 확장제로 작용하여 모낭으로의 혈류를 증가시키고 모발 성장을 촉진한다.</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>Androgen receptor signaling, DHT synthesis, Hair follicle cycling (anagen, catagen, telogen)</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>Hair follicle cells, Dermal papilla cells, Stumptail macaque (animal model)</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>피나스테리드(1mg) 및 듀타스테리드는 FDA 승인 경구 치료제이며, 미녹시딜(2-5%)은 국소 치료제로 안드로겐성 탈모증의 치료에 효과적이다. 5% 미녹시딜은 2% 제제 대비 48주 후 48% 더 많은 모발 재성장을 나타냈으며, 병합 치료가 단일 치료보다 더 우수한 효과를 보인다. 두타스테리드는 Type 1과 Type 2 5-알파 환원효소 모두를 억제하여 피나스테리드보다 더 강력한 DHT 억제 효과를 나타낸다.</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>DHT, Hair count/density, Hair loss area</t>
+        </is>
+      </c>
+      <c r="K1057" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>10564722_Molecular cloning of canine bullous pemphigoid ant.txt</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Preclinical</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr"/>
+      <c r="E1058" t="inlineStr"/>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="inlineStr"/>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>Canine keratinocyte cell line (papillomavirus-immortalized), Canine squamous carcinoma cell line SCC 2/88</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr"/>
+      <c r="J1058" t="inlineStr"/>
+      <c r="K1058" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>10583042_The psychosocial consequences of androgenetic alop.txt</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>5-alpha reductase, Androgen receptor</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>Finasteride, Dutasteride, Minoxidil, Rosemary oil, Melatonin, Watercress, Marine complex, Procyanidin, Saw palmetto, Pumpkin seed oil, Rice bran extract</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>피나스테리드와 두타스테리드는 5-알파 리덕타제 억제제로 안드로겐 의존적 메커니즘을 통해 작용하며, 미녹시딜은 안드로겐 대사와 무관하게 작용한다. 대체 치료제들은 다양한 메커니즘을 통해 모발 밀도 증가에 기여한다.</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>Androgen metabolism, DHT signaling</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr"/>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>네트워크 메타분석 결과 경구 두타스테리드, 국소/경구 미녹시딜, 경구/국소 피나스테리드 등 기존 단독 치료가 남성 AGA에 효과적임을 확인했다. 로즈마리 오일(국소)과 멜라토닌(국소) 등 일부 대체 제품도 기존 치료와 비교하여 상대적 효능에 대한 증거를 제공한다.</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>Total hair density (hairs/cm²), Hair count at 24 weeks</t>
+        </is>
+      </c>
+      <c r="K1059" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
